--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488084_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488084_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.7706</v>
+        <v>9.5283</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4759</v>
+        <v>6.374</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2947</v>
+        <v>3.1543</v>
       </c>
       <c r="G2" t="n">
         <v>7.545</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2851</v>
+        <v>2.0428</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2262</v>
+        <v>1.1244</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0589</v>
+        <v>0.9185</v>
       </c>
       <c r="V2" t="n">
         <v>0.337</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7995</v>
+        <v>7.3816</v>
       </c>
       <c r="E3" t="n">
-        <v>5.196</v>
+        <v>4.8904</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6035</v>
+        <v>2.4912</v>
       </c>
       <c r="G3" t="n">
         <v>5.7733</v>
@@ -688,13 +688,13 @@
         <v>0.7929</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4999</v>
+        <v>1.082</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7343</v>
+        <v>0.4287</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6533</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2666</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6948</v>
+        <v>5.621</v>
       </c>
       <c r="E4" t="n">
-        <v>2.756</v>
+        <v>2.6542</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9388</v>
+        <v>2.9668</v>
       </c>
       <c r="G4" t="n">
         <v>3.1674</v>
@@ -766,13 +766,13 @@
         <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0209</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9766</v>
+        <v>0.8748</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0442</v>
+        <v>0.0723</v>
       </c>
       <c r="V4" t="n">
         <v>-0.674</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1079</v>
+        <v>5.1568</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4738</v>
+        <v>3.2701</v>
       </c>
       <c r="F5" t="n">
-        <v>1.634</v>
+        <v>1.8867</v>
       </c>
       <c r="G5" t="n">
         <v>3.0379</v>
@@ -844,13 +844,13 @@
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6714</v>
+        <v>0.7204</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7343</v>
+        <v>0.5305</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06279999999999999</v>
+        <v>0.1899</v>
       </c>
       <c r="V5" t="n">
         <v>0.4074</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.0799</v>
+        <v>4.2794</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8114</v>
+        <v>0.4039</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2685</v>
+        <v>3.8754</v>
       </c>
       <c r="G6" t="n">
         <v>0.8003</v>
@@ -922,13 +922,13 @@
         <v>2.1805</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2707</v>
+        <v>1.4701</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1638</v>
+        <v>0.7564</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1069</v>
+        <v>0.7138</v>
       </c>
       <c r="V6" t="n">
         <v>1.8107</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.0196</v>
+        <v>3.9721</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0847</v>
+        <v>1.2243</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9350000000000001</v>
+        <v>2.7478</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1487</v>
+        <v>-0.493</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3031</v>
+        <v>1.005</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8455</v>
+        <v>-1.498</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9009</v>
+        <v>-1.6067</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4193</v>
+        <v>0.9893</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5184</v>
+        <v>-2.596</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2478</v>
+        <v>1.1137</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1162</v>
+        <v>0.0157</v>
       </c>
       <c r="O7" t="n">
-        <v>1.364</v>
+        <v>1.098</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8094</v>
+        <v>1.3352</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9678</v>
+        <v>0.4168</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1583</v>
+        <v>0.9185</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5331</v>
+        <v>1.5441</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>2.4142</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7403</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5013</v>
+        <v>3.1518</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6131</v>
+        <v>1.9641</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8882</v>
+        <v>1.1877</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.493</v>
+        <v>2.1487</v>
       </c>
       <c r="H8" t="n">
-        <v>1.005</v>
+        <v>1.3031</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.498</v>
+        <v>0.8455</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6067</v>
+        <v>0.9009</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9893</v>
+        <v>1.4193</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.596</v>
+        <v>-0.5184</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1137</v>
+        <v>1.2478</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0157</v>
+        <v>-0.1162</v>
       </c>
       <c r="O8" t="n">
-        <v>1.098</v>
+        <v>1.364</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
         <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.9416</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1944</v>
+        <v>0.8472</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0589</v>
+        <v>0.0944</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5441</v>
+        <v>-0.5331</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4142</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8701</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9218</v>
+        <v>3.109</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6092</v>
+        <v>-0.5905</v>
       </c>
       <c r="F9" t="n">
-        <v>3.531</v>
+        <v>3.6995</v>
       </c>
       <c r="G9" t="n">
         <v>0.6936</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0389</v>
+        <v>1.2261</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1944</v>
+        <v>0.8243</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2333</v>
+        <v>0.4018</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1804</v>
+        <v>1.5598</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3492</v>
+        <v>0.7567</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8312</v>
+        <v>0.8032</v>
       </c>
       <c r="G10" t="n">
         <v>0.8761</v>
@@ -1234,13 +1234,13 @@
         <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0921</v>
+        <v>0.2873</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2496</v>
+        <v>0.1579</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1574</v>
+        <v>0.1294</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6143999999999999</v>
+        <v>1.078</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6789</v>
+        <v>-1.2715</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2933</v>
+        <v>2.3495</v>
       </c>
       <c r="G11" t="n">
         <v>0.5374</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0175</v>
+        <v>1.4812</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5471</v>
+        <v>0.9546</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4704</v>
+        <v>0.5266</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9405</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0624</v>
+        <v>-0.4699</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0624</v>
+        <v>-0.4699</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1468,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4809</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6167</v>
+        <v>0.2093</v>
       </c>
       <c r="U13" t="n">
         <v>-0.1358</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9354</v>
+        <v>-0.6755</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.5051</v>
+        <v>-1.3014</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5697</v>
+        <v>0.6259</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0463</v>
@@ -1546,13 +1546,13 @@
         <v>0.3964</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2856</v>
+        <v>-0.0257</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1872</v>
+        <v>0.0165</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>43.9951</v>
+        <v>43.99510000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>18.20720000000001</v>
+        <v>18.2071</v>
       </c>
       <c r="F15" t="n">
-        <v>25.7879</v>
+        <v>25.788</v>
       </c>
       <c r="G15" t="n">
         <v>22.79980000000001</v>
@@ -1624,13 +1624,13 @@
         <v>15.8579</v>
       </c>
       <c r="S15" t="n">
-        <v>11.5814</v>
+        <v>11.5815</v>
       </c>
       <c r="T15" t="n">
-        <v>7.1412</v>
+        <v>7.1414</v>
       </c>
       <c r="U15" t="n">
-        <v>4.440300000000001</v>
+        <v>4.4405</v>
       </c>
       <c r="V15" t="n">
         <v>1.685</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.946</v>
+        <v>1.1673</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9413</v>
+        <v>3.2469</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9953</v>
+        <v>-2.0796</v>
       </c>
       <c r="G16" t="n">
         <v>0.1562</v>
@@ -1702,13 +1702,13 @@
         <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2786</v>
+        <v>-1.0572</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3426</v>
+        <v>-0.4269</v>
       </c>
       <c r="V16" t="n">
         <v>1.4737</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.2642</v>
+        <v>-3.9534</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1371</v>
+        <v>-2.9521</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.127</v>
+        <v>-1.0013</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1481</v>
+        <v>-2.3974</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8333</v>
+        <v>-1.1423</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9814000000000001</v>
+        <v>-1.2551</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9666</v>
+        <v>-1.0352</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4326</v>
+        <v>0.9218</v>
       </c>
       <c r="L18" t="n">
-        <v>0.534</v>
+        <v>-1.957</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8185</v>
+        <v>-1.3622</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2659</v>
+        <v>-2.0641</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4474</v>
+        <v>0.7019</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.7751</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6372</v>
+        <v>-2.23</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1393</v>
+        <v>-0.9258</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4979</v>
+        <v>-1.3042</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.7155</v>
+        <v>-3.9834</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4615</v>
+        <v>-2.1371</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.254</v>
+        <v>-1.8462</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3974</v>
+        <v>0.1481</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1423</v>
+        <v>-0.8333</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2551</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0352</v>
+        <v>1.9666</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9218</v>
+        <v>1.4326</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.957</v>
+        <v>0.534</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3622</v>
+        <v>-1.8185</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0641</v>
+        <v>-2.2659</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7019</v>
+        <v>0.4474</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.9921</v>
+        <v>-1.3564</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4351</v>
+        <v>-0.1393</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5569</v>
+        <v>-1.2171</v>
       </c>
       <c r="V19" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. GARCIA GARRIDO</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8175</v>
+        <v>-4.4122</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0442</v>
+        <v>-2.1735</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7733</v>
+        <v>-2.2387</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4356</v>
+        <v>-1.8628</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8578</v>
+        <v>-2.6433</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5778</v>
+        <v>0.7805</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2538</v>
+        <v>0.2409</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.659</v>
+        <v>-0.3696</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5949</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1818</v>
+        <v>-2.1037</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1989</v>
+        <v>-2.2737</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0171</v>
+        <v>0.17</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.784</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5275</v>
+        <v>-2.0914</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0552</v>
+        <v>-0.9653</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5826</v>
+        <v>-1.1262</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.0704</v>
+        <v>0.5331</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1367</v>
+        <v>0.5331</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>F. GARCIA GARRIDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0162</v>
+        <v>-5.0389</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5809</v>
+        <v>-2.3498</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4353</v>
+        <v>-2.6891</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8628</v>
+        <v>-2.4356</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6433</v>
+        <v>-1.8578</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7805</v>
+        <v>-0.5778</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2409</v>
+        <v>-1.2538</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3696</v>
+        <v>-0.659</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6104000000000001</v>
+        <v>-0.5949</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1037</v>
+        <v>-1.1818</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2737</v>
+        <v>-1.1989</v>
       </c>
       <c r="O21" t="n">
-        <v>0.17</v>
+        <v>0.0171</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9911</v>
+        <v>-1.784</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6955</v>
+        <v>-0.7489</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3727</v>
+        <v>-0.2505</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.3227</v>
+        <v>-0.4984</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5331</v>
+        <v>-0.0704</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5331</v>
+        <v>1.1367</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7249</v>
+        <v>-6.1533</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2268</v>
+        <v>-2.4305</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4982</v>
+        <v>-3.7228</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4351</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-1.1325</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.132</v>
+        <v>-0.3358</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-0.7967</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8107</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.4124</v>
+        <v>-6.4228</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7422</v>
+        <v>-5.6403</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6702</v>
+        <v>-0.7825</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4109</v>
@@ -2248,13 +2248,13 @@
         <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5961</v>
+        <v>-0.6066</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5064</v>
+        <v>-0.4045</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0897</v>
+        <v>-0.202</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2071</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2892</v>
+        <v>-7.851</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4008</v>
+        <v>-5.4541</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8883</v>
+        <v>-2.3969</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.1784</v>
+        <v>-6.9892</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.1255</v>
+        <v>-5.2481</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.053</v>
+        <v>-1.7411</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.422</v>
+        <v>-4.9689</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-2.3729</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.6362</v>
+        <v>-2.596</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7565</v>
+        <v>-2.0203</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.3397</v>
+        <v>-2.8751</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.8549</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5858</v>
+        <v>1.5858</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1176</v>
+        <v>-1.5775</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2017</v>
+        <v>-0.4852</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08409999999999999</v>
+        <v>-1.0923</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4074</v>
+        <v>-0.8701</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6036</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.3064</v>
+        <v>-7.9526</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.7411</v>
+        <v>-6.5027</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5654</v>
+        <v>-1.4499</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.9892</v>
+        <v>-5.1784</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.2481</v>
+        <v>-3.1255</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.7411</v>
+        <v>-2.053</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.9689</v>
+        <v>-3.422</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.3729</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.596</v>
+        <v>-2.6362</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0203</v>
+        <v>-1.7565</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.8751</v>
+        <v>-2.3397</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8549</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>1.5858</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0329</v>
+        <v>-0.781</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2279</v>
+        <v>-0.3035</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.2608</v>
+        <v>-0.4775</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.8701</v>
+        <v>-0.4074</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.8701</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="26">
@@ -2440,7 +2440,7 @@
         <v>-43.995</v>
       </c>
       <c r="E26" t="n">
-        <v>-25.788</v>
+        <v>-25.7879</v>
       </c>
       <c r="F26" t="n">
         <v>-18.207</v>
@@ -2470,10 +2470,10 @@
         <v>-17.6928</v>
       </c>
       <c r="O26" t="n">
-        <v>3.652100000000001</v>
+        <v>3.6521</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.928800000000002</v>
+        <v>-7.928800000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-15.8577</v>
@@ -2482,13 +2482,13 @@
         <v>7.928900000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-11.5816</v>
+        <v>-11.5815</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.4401</v>
+        <v>-4.4403</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.1412</v>
+        <v>-7.1413</v>
       </c>
       <c r="V26" t="n">
         <v>-1.6849</v>
